--- a/ACCY122/Assessment II/Oceanview Pilates Studio  - Calculation.xlsx
+++ b/ACCY122/Assessment II/Oceanview Pilates Studio  - Calculation.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10412"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\josep\Desktop\SIM-UOW-Mods\ACCY122\Assessment II\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/joseph/Desktop/SIM-UOW-Mods/ACCY122/Assessment II/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C4451756-78B3-4923-8C91-B2FFF2AB7F43}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D679934F-6734-8349-BE83-A4234EEE4C3A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="500" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Journal" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="314" uniqueCount="130">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="310" uniqueCount="130">
   <si>
     <t>Ref</t>
   </si>
@@ -747,6 +747,24 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -755,24 +773,6 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1169,18 +1169,18 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="B1:L54"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7" style="1" customWidth="1"/>
-    <col min="2" max="3" width="9.140625" style="1"/>
-    <col min="4" max="4" width="71.42578125" style="1" customWidth="1"/>
-    <col min="5" max="9" width="9.140625" style="1"/>
-    <col min="10" max="10" width="69.7109375" style="1" customWidth="1"/>
-    <col min="11" max="16384" width="9.140625" style="1"/>
+    <col min="2" max="3" width="9.1640625" style="1"/>
+    <col min="4" max="4" width="71.5" style="1" customWidth="1"/>
+    <col min="5" max="9" width="9.1640625" style="1"/>
+    <col min="10" max="10" width="69.6640625" style="1" customWidth="1"/>
+    <col min="11" max="16384" width="9.1640625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="2" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="1" spans="2:12" ht="16" thickBot="1" x14ac:dyDescent="0.25"/>
+    <row r="2" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B2" s="52" t="s">
         <v>3</v>
       </c>
@@ -1196,7 +1196,7 @@
       <c r="K2" s="53"/>
       <c r="L2" s="54"/>
     </row>
-    <row r="3" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B3" s="5" t="s">
         <v>0</v>
       </c>
@@ -1228,7 +1228,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="4" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B4" s="5">
         <v>1</v>
       </c>
@@ -1256,7 +1256,7 @@
       </c>
       <c r="L4" s="6"/>
     </row>
-    <row r="5" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B5" s="5"/>
       <c r="D5" s="8" t="s">
         <v>24</v>
@@ -1272,7 +1272,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="6" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B6" s="5"/>
       <c r="D6" s="9" t="s">
         <v>5</v>
@@ -1284,7 +1284,7 @@
       </c>
       <c r="L6" s="6"/>
     </row>
-    <row r="7" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B7" s="5">
         <v>2</v>
       </c>
@@ -1312,7 +1312,7 @@
       </c>
       <c r="L7" s="6"/>
     </row>
-    <row r="8" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B8" s="5"/>
       <c r="D8" s="8" t="s">
         <v>10</v>
@@ -1328,7 +1328,7 @@
         <v>700</v>
       </c>
     </row>
-    <row r="9" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B9" s="5"/>
       <c r="D9" s="9" t="s">
         <v>28</v>
@@ -1340,7 +1340,7 @@
       </c>
       <c r="L9" s="6"/>
     </row>
-    <row r="10" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B10" s="5">
         <v>3</v>
       </c>
@@ -1368,7 +1368,7 @@
       </c>
       <c r="L10" s="6"/>
     </row>
-    <row r="11" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B11" s="5"/>
       <c r="D11" s="8" t="s">
         <v>12</v>
@@ -1384,7 +1384,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="12" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B12" s="5"/>
       <c r="C12" s="7"/>
       <c r="D12" s="9" t="s">
@@ -1398,7 +1398,7 @@
       </c>
       <c r="L12" s="6"/>
     </row>
-    <row r="13" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B13" s="5">
         <v>4</v>
       </c>
@@ -1426,7 +1426,7 @@
       </c>
       <c r="L13" s="6"/>
     </row>
-    <row r="14" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B14" s="5"/>
       <c r="D14" s="8" t="s">
         <v>10</v>
@@ -1442,7 +1442,7 @@
         <v>1200</v>
       </c>
     </row>
-    <row r="15" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B15" s="5"/>
       <c r="D15" s="8" t="s">
         <v>12</v>
@@ -1456,7 +1456,7 @@
       </c>
       <c r="L15" s="6"/>
     </row>
-    <row r="16" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B16" s="5"/>
       <c r="D16" s="9" t="s">
         <v>30</v>
@@ -1476,7 +1476,7 @@
       </c>
       <c r="L16" s="6"/>
     </row>
-    <row r="17" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B17" s="5">
         <v>5</v>
       </c>
@@ -1499,7 +1499,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="18" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B18" s="5"/>
       <c r="D18" s="8" t="s">
         <v>14</v>
@@ -1513,7 +1513,7 @@
       </c>
       <c r="L18" s="6"/>
     </row>
-    <row r="19" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B19" s="5"/>
       <c r="D19" s="9" t="s">
         <v>15</v>
@@ -1523,7 +1523,7 @@
       <c r="J19" s="2"/>
       <c r="L19" s="6"/>
     </row>
-    <row r="20" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:12" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B20" s="5">
         <v>6</v>
       </c>
@@ -1550,7 +1550,7 @@
         <v>3200</v>
       </c>
     </row>
-    <row r="21" spans="2:12" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="2:12" ht="17" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B21" s="5"/>
       <c r="D21" s="8" t="s">
         <v>10</v>
@@ -1564,14 +1564,14 @@
       <c r="K21" s="12"/>
       <c r="L21" s="15"/>
     </row>
-    <row r="22" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B22" s="5"/>
       <c r="D22" s="9" t="s">
         <v>16</v>
       </c>
       <c r="F22" s="6"/>
     </row>
-    <row r="23" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B23" s="5">
         <v>7</v>
       </c>
@@ -1586,7 +1586,7 @@
       </c>
       <c r="F23" s="6"/>
     </row>
-    <row r="24" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B24" s="5"/>
       <c r="D24" s="8" t="s">
         <v>17</v>
@@ -1595,14 +1595,14 @@
         <v>6000</v>
       </c>
     </row>
-    <row r="25" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B25" s="5"/>
       <c r="D25" s="9" t="s">
         <v>31</v>
       </c>
       <c r="F25" s="6"/>
     </row>
-    <row r="26" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B26" s="5">
         <v>8</v>
       </c>
@@ -1617,7 +1617,7 @@
       </c>
       <c r="F26" s="6"/>
     </row>
-    <row r="27" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B27" s="5"/>
       <c r="D27" s="8" t="s">
         <v>13</v>
@@ -1626,14 +1626,14 @@
         <v>5500</v>
       </c>
     </row>
-    <row r="28" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B28" s="5"/>
       <c r="D28" s="9" t="s">
         <v>18</v>
       </c>
       <c r="F28" s="6"/>
     </row>
-    <row r="29" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="29" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B29" s="5">
         <v>9</v>
       </c>
@@ -1648,7 +1648,7 @@
       </c>
       <c r="F29" s="6"/>
     </row>
-    <row r="30" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="30" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B30" s="5"/>
       <c r="D30" s="8" t="s">
         <v>14</v>
@@ -1657,14 +1657,14 @@
         <v>3200</v>
       </c>
     </row>
-    <row r="31" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="31" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B31" s="5"/>
       <c r="D31" s="9" t="s">
         <v>19</v>
       </c>
       <c r="F31" s="6"/>
     </row>
-    <row r="32" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B32" s="5">
         <v>10</v>
       </c>
@@ -1679,7 +1679,7 @@
       </c>
       <c r="F32" s="6"/>
     </row>
-    <row r="33" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="33" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B33" s="5"/>
       <c r="D33" s="8" t="s">
         <v>10</v>
@@ -1688,14 +1688,14 @@
         <v>600</v>
       </c>
     </row>
-    <row r="34" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="34" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B34" s="5"/>
       <c r="D34" s="9" t="s">
         <v>20</v>
       </c>
       <c r="F34" s="6"/>
     </row>
-    <row r="35" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="35" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B35" s="5">
         <v>11</v>
       </c>
@@ -1710,7 +1710,7 @@
       </c>
       <c r="F35" s="6"/>
     </row>
-    <row r="36" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="36" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B36" s="5"/>
       <c r="D36" s="8" t="s">
         <v>21</v>
@@ -1719,14 +1719,14 @@
         <v>2400</v>
       </c>
     </row>
-    <row r="37" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="37" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B37" s="5"/>
       <c r="D37" s="9" t="s">
         <v>26</v>
       </c>
       <c r="F37" s="6"/>
     </row>
-    <row r="38" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="38" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B38" s="5">
         <v>12</v>
       </c>
@@ -1741,7 +1741,7 @@
       </c>
       <c r="F38" s="6"/>
     </row>
-    <row r="39" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="39" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B39" s="5"/>
       <c r="D39" s="8" t="s">
         <v>10</v>
@@ -1750,14 +1750,14 @@
         <v>2200</v>
       </c>
     </row>
-    <row r="40" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="40" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B40" s="5"/>
       <c r="D40" s="9" t="s">
         <v>16</v>
       </c>
       <c r="F40" s="6"/>
     </row>
-    <row r="41" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="41" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B41" s="5">
         <v>13</v>
       </c>
@@ -1772,7 +1772,7 @@
       </c>
       <c r="F41" s="6"/>
     </row>
-    <row r="42" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="42" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B42" s="5"/>
       <c r="D42" s="2" t="s">
         <v>10</v>
@@ -1781,7 +1781,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="43" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="43" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B43" s="5"/>
       <c r="C43" s="1" t="s">
         <v>9</v>
@@ -1791,7 +1791,7 @@
       </c>
       <c r="F43" s="6"/>
     </row>
-    <row r="44" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="44" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B44" s="5">
         <v>14</v>
       </c>
@@ -1806,7 +1806,7 @@
       </c>
       <c r="F44" s="6"/>
     </row>
-    <row r="45" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="45" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B45" s="5"/>
       <c r="D45" s="10" t="s">
         <v>10</v>
@@ -1815,19 +1815,19 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="46" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="46" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B46" s="5"/>
       <c r="D46" s="9" t="s">
         <v>25</v>
       </c>
       <c r="F46" s="6"/>
     </row>
-    <row r="47" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="47" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B47" s="5"/>
       <c r="D47" s="2"/>
       <c r="F47" s="6"/>
     </row>
-    <row r="48" spans="2:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="2:6" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B48" s="5"/>
       <c r="D48" s="2" t="s">
         <v>33</v>
@@ -1841,34 +1841,34 @@
         <v>65400</v>
       </c>
     </row>
-    <row r="49" spans="2:6" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="2:6" ht="17" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B49" s="11"/>
       <c r="C49" s="12"/>
       <c r="D49" s="12"/>
       <c r="E49" s="12"/>
       <c r="F49" s="15"/>
     </row>
-    <row r="50" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="50" spans="2:6" x14ac:dyDescent="0.2">
       <c r="D50" s="2"/>
     </row>
-    <row r="51" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="51" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B51" s="2" t="s">
         <v>27</v>
       </c>
       <c r="D51" s="2"/>
     </row>
-    <row r="52" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="52" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B52" s="3" t="s">
         <v>34</v>
       </c>
       <c r="D52" s="2"/>
     </row>
-    <row r="53" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="53" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B53" s="3" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="54" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="54" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B54" s="3" t="s">
         <v>46</v>
       </c>
@@ -1887,24 +1887,24 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CA8E1411-F875-4BCF-A6DF-12BD20567178}">
   <dimension ref="B1:O50"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="2" max="2" width="11.85546875" customWidth="1"/>
+    <col min="2" max="2" width="11.83203125" customWidth="1"/>
     <col min="3" max="3" width="23" customWidth="1"/>
     <col min="6" max="6" width="5" customWidth="1"/>
-    <col min="8" max="8" width="40.42578125" customWidth="1"/>
-    <col min="11" max="11" width="4.140625" customWidth="1"/>
-    <col min="13" max="13" width="24.140625" customWidth="1"/>
+    <col min="8" max="8" width="40.5" customWidth="1"/>
+    <col min="11" max="11" width="4.1640625" customWidth="1"/>
+    <col min="13" max="13" width="24.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="2" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B2" s="55" t="s">
+    <row r="1" spans="2:15" ht="16" thickBot="1" x14ac:dyDescent="0.25"/>
+    <row r="2" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="B2" s="49" t="s">
         <v>58</v>
       </c>
-      <c r="C2" s="56"/>
-      <c r="D2" s="56"/>
-      <c r="E2" s="57"/>
+      <c r="C2" s="50"/>
+      <c r="D2" s="50"/>
+      <c r="E2" s="51"/>
       <c r="G2" s="27" t="s">
         <v>61</v>
       </c>
@@ -1918,7 +1918,7 @@
       <c r="N2" s="28"/>
       <c r="O2" s="29"/>
     </row>
-    <row r="3" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B3" s="17" t="s">
         <v>1</v>
       </c>
@@ -1956,7 +1956,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="4" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B4" s="18">
         <v>46235</v>
       </c>
@@ -1987,7 +1987,7 @@
         <v>5500</v>
       </c>
     </row>
-    <row r="5" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B5" s="18">
         <v>46235</v>
       </c>
@@ -2018,7 +2018,7 @@
         <v>3200</v>
       </c>
     </row>
-    <row r="6" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:15" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B6" s="22">
         <v>46239</v>
       </c>
@@ -2039,17 +2039,18 @@
       <c r="J6" s="31">
         <v>20000</v>
       </c>
-      <c r="L6" s="22">
+      <c r="L6" s="24">
         <v>46265</v>
       </c>
-      <c r="M6" s="2" t="s">
+      <c r="M6" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="O6" s="6">
+      <c r="N6" s="30"/>
+      <c r="O6" s="15">
         <v>1200</v>
       </c>
     </row>
-    <row r="7" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:15" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B7" s="22">
         <v>46246</v>
       </c>
@@ -2060,18 +2061,12 @@
       <c r="E7" s="21">
         <v>2200</v>
       </c>
-      <c r="L7" s="22">
-        <v>46265</v>
-      </c>
-      <c r="M7" s="19" t="s">
-        <v>54</v>
-      </c>
+      <c r="L7" s="32"/>
+      <c r="M7" s="19"/>
       <c r="N7" s="20"/>
-      <c r="O7" s="21">
-        <v>9900</v>
-      </c>
-    </row>
-    <row r="8" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="O7" s="20"/>
+    </row>
+    <row r="8" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B8" s="22">
         <v>46249</v>
       </c>
@@ -2088,18 +2083,11 @@
       <c r="H8" s="28"/>
       <c r="I8" s="28"/>
       <c r="J8" s="29"/>
-      <c r="L8" s="24">
-        <v>46266</v>
-      </c>
-      <c r="M8" s="13" t="s">
-        <v>55</v>
-      </c>
-      <c r="N8" s="30"/>
-      <c r="O8" s="31">
-        <v>9900</v>
-      </c>
-    </row>
-    <row r="9" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L8" s="32"/>
+      <c r="M8" s="2"/>
+      <c r="O8" s="20"/>
+    </row>
+    <row r="9" spans="2:15" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B9" s="22">
         <v>46252</v>
       </c>
@@ -2123,7 +2111,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="10" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B10" s="22">
         <v>46254</v>
       </c>
@@ -2151,7 +2139,7 @@
       <c r="N10" s="28"/>
       <c r="O10" s="29"/>
     </row>
-    <row r="11" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B11" s="18">
         <v>46256</v>
       </c>
@@ -2185,7 +2173,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="12" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B12" s="18">
         <v>46259</v>
       </c>
@@ -2216,7 +2204,7 @@
         <v>6000</v>
       </c>
     </row>
-    <row r="13" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B13" s="18">
         <v>46260</v>
       </c>
@@ -2248,7 +2236,7 @@
         <v>6000</v>
       </c>
     </row>
-    <row r="14" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="2:15" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B14" s="18">
         <v>46262</v>
       </c>
@@ -2280,7 +2268,7 @@
         <v>6000</v>
       </c>
     </row>
-    <row r="15" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="2:15" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B15" s="18">
         <v>46265</v>
       </c>
@@ -2296,7 +2284,7 @@
       <c r="I15" s="20"/>
       <c r="J15" s="20"/>
     </row>
-    <row r="16" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B16" s="22">
         <v>46265</v>
       </c>
@@ -2320,7 +2308,7 @@
       <c r="N16" s="28"/>
       <c r="O16" s="29"/>
     </row>
-    <row r="17" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:15" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B17" s="17"/>
       <c r="D17" s="16">
         <f>SUM(D4:D16)</f>
@@ -2355,7 +2343,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="18" spans="2:15" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:15" ht="17" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B18" s="24">
         <v>46266</v>
       </c>
@@ -2387,7 +2375,7 @@
       </c>
       <c r="O18" s="26"/>
     </row>
-    <row r="19" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:15" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="G19" s="33">
         <v>46252</v>
       </c>
@@ -2399,7 +2387,7 @@
         <v>5500</v>
       </c>
     </row>
-    <row r="20" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:15" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B20" s="27" t="s">
         <v>57</v>
       </c>
@@ -2413,7 +2401,7 @@
       <c r="N20" s="28"/>
       <c r="O20" s="29"/>
     </row>
-    <row r="21" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B21" s="17" t="s">
         <v>1</v>
       </c>
@@ -2445,7 +2433,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="22" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B22" s="18">
         <v>46235</v>
       </c>
@@ -2479,7 +2467,7 @@
         <v>2400</v>
       </c>
     </row>
-    <row r="23" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B23" s="22">
         <v>46265</v>
       </c>
@@ -2511,7 +2499,7 @@
       </c>
       <c r="O23" s="21"/>
     </row>
-    <row r="24" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B24" s="22">
         <v>46265</v>
       </c>
@@ -2543,7 +2531,7 @@
       </c>
       <c r="O24" s="21"/>
     </row>
-    <row r="25" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="2:15" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B25" s="17"/>
       <c r="D25" s="16">
         <v>3000</v>
@@ -2569,7 +2557,7 @@
         <v>2400</v>
       </c>
     </row>
-    <row r="26" spans="2:15" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="2:15" ht="17" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B26" s="24">
         <v>46266</v>
       </c>
@@ -2597,8 +2585,8 @@
         <v>1200</v>
       </c>
     </row>
-    <row r="27" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="28" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:15" ht="16" thickBot="1" x14ac:dyDescent="0.25"/>
+    <row r="28" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B28" s="27" t="s">
         <v>59</v>
       </c>
@@ -2618,7 +2606,7 @@
       <c r="N28" s="28"/>
       <c r="O28" s="29"/>
     </row>
-    <row r="29" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="29" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B29" s="17" t="s">
         <v>1</v>
       </c>
@@ -2656,7 +2644,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="30" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="30" spans="2:15" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B30" s="18">
         <v>46238</v>
       </c>
@@ -2676,18 +2664,18 @@
       <c r="J30" s="21">
         <v>600</v>
       </c>
-      <c r="L30" s="18">
+      <c r="L30" s="33">
         <v>46265</v>
       </c>
-      <c r="M30" t="s">
+      <c r="M30" s="30" t="s">
         <v>10</v>
       </c>
-      <c r="N30" s="20">
+      <c r="N30" s="25">
         <v>1000</v>
       </c>
-      <c r="O30" s="35"/>
-    </row>
-    <row r="31" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="O30" s="26"/>
+    </row>
+    <row r="31" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B31" s="22">
         <v>46265</v>
       </c>
@@ -2707,18 +2695,11 @@
       <c r="J31" s="21">
         <v>600</v>
       </c>
-      <c r="L31" s="22">
-        <v>46265</v>
-      </c>
-      <c r="M31" s="19" t="s">
-        <v>54</v>
-      </c>
-      <c r="N31" s="20">
-        <v>1000</v>
-      </c>
-      <c r="O31" s="35"/>
-    </row>
-    <row r="32" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L31" s="32"/>
+      <c r="M31" s="19"/>
+      <c r="N31" s="20"/>
+    </row>
+    <row r="32" spans="2:15" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B32" s="22">
         <v>46265</v>
       </c>
@@ -2739,18 +2720,11 @@
       <c r="J32" s="31">
         <v>600</v>
       </c>
-      <c r="L32" s="24">
-        <v>46266</v>
-      </c>
-      <c r="M32" s="13" t="s">
-        <v>55</v>
-      </c>
-      <c r="N32" s="25">
-        <v>1000</v>
-      </c>
-      <c r="O32" s="26"/>
-    </row>
-    <row r="33" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L32" s="32"/>
+      <c r="M32" s="2"/>
+      <c r="N32" s="20"/>
+    </row>
+    <row r="33" spans="2:15" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B33" s="17"/>
       <c r="D33" s="16">
         <v>1200</v>
@@ -2759,7 +2733,7 @@
         <v>1200</v>
       </c>
     </row>
-    <row r="34" spans="2:15" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="2:15" ht="17" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B34" s="24">
         <v>46266</v>
       </c>
@@ -2783,7 +2757,7 @@
       <c r="N34" s="28"/>
       <c r="O34" s="29"/>
     </row>
-    <row r="35" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="2:15" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="G35" s="17" t="s">
         <v>1</v>
       </c>
@@ -2809,7 +2783,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="36" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="2:15" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B36" s="27" t="s">
         <v>60</v>
       </c>
@@ -2837,7 +2811,7 @@
       </c>
       <c r="O36" s="26"/>
     </row>
-    <row r="37" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="2:15" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B37" s="17" t="s">
         <v>1</v>
       </c>
@@ -2853,7 +2827,7 @@
       <c r="I37" s="1"/>
       <c r="J37" s="1"/>
     </row>
-    <row r="38" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="38" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B38" s="18">
         <v>46239</v>
       </c>
@@ -2877,7 +2851,7 @@
       <c r="N38" s="28"/>
       <c r="O38" s="29"/>
     </row>
-    <row r="39" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="39" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B39" s="18">
         <v>46239</v>
       </c>
@@ -2913,7 +2887,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="40" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="2:15" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B40" s="22">
         <v>46265</v>
       </c>
@@ -2930,10 +2904,10 @@
       <c r="H40" t="s">
         <v>71</v>
       </c>
-      <c r="I40" s="1">
+      <c r="I40" s="1"/>
+      <c r="J40" s="21">
         <v>200</v>
       </c>
-      <c r="J40" s="21"/>
       <c r="L40" s="24">
         <v>46265</v>
       </c>
@@ -2945,7 +2919,7 @@
       </c>
       <c r="O40" s="26"/>
     </row>
-    <row r="41" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="2:15" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B41" s="24">
         <v>46266</v>
       </c>
@@ -2962,68 +2936,68 @@
       <c r="H41" s="19" t="s">
         <v>54</v>
       </c>
-      <c r="I41" s="20">
+      <c r="I41" s="20"/>
+      <c r="J41" s="21">
         <v>200</v>
       </c>
-      <c r="J41" s="21"/>
-    </row>
-    <row r="42" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="42" spans="2:15" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="G42" s="24">
         <v>46266</v>
       </c>
       <c r="H42" s="13" t="s">
         <v>55</v>
       </c>
-      <c r="I42" s="25">
+      <c r="I42" s="25"/>
+      <c r="J42" s="31">
         <v>200</v>
       </c>
-      <c r="J42" s="31"/>
-    </row>
-    <row r="43" spans="2:15" x14ac:dyDescent="0.25">
+    </row>
+    <row r="43" spans="2:15" x14ac:dyDescent="0.2">
       <c r="G43" s="32"/>
       <c r="H43" s="19"/>
       <c r="I43" s="20"/>
       <c r="J43" s="20"/>
     </row>
-    <row r="44" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="44" spans="2:15" x14ac:dyDescent="0.2">
       <c r="G44" s="32"/>
       <c r="H44" s="2"/>
       <c r="I44" s="20"/>
       <c r="J44" s="20"/>
     </row>
-    <row r="45" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="45" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B45" s="2" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="46" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="46" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B46" s="3" t="s">
         <v>102</v>
       </c>
       <c r="D46" s="1"/>
       <c r="E46" s="1"/>
     </row>
-    <row r="47" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="47" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B47" s="3" t="s">
         <v>104</v>
       </c>
       <c r="D47" s="1"/>
       <c r="E47" s="1"/>
     </row>
-    <row r="48" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="48" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B48" s="46" t="s">
         <v>103</v>
       </c>
       <c r="D48" s="1"/>
       <c r="E48" s="20"/>
     </row>
-    <row r="49" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="49" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B49" s="32"/>
       <c r="C49" s="19"/>
       <c r="D49" s="20"/>
       <c r="E49" s="20"/>
     </row>
-    <row r="50" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="50" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B50" s="32"/>
       <c r="C50" s="2"/>
       <c r="D50" s="20"/>
@@ -3040,21 +3014,21 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2483F31C-F792-48EB-B93F-5257B81B8823}">
   <dimension ref="B1:F26"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="2" max="2" width="49.42578125" customWidth="1"/>
-    <col min="6" max="6" width="18.140625" style="20" customWidth="1"/>
+    <col min="2" max="2" width="49.5" customWidth="1"/>
+    <col min="6" max="6" width="18.1640625" style="20" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="2" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B2" s="49" t="s">
+    <row r="1" spans="2:6" ht="16" thickBot="1" x14ac:dyDescent="0.25"/>
+    <row r="2" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B2" s="55" t="s">
         <v>75</v>
       </c>
-      <c r="C2" s="50"/>
-      <c r="D2" s="51"/>
-    </row>
-    <row r="3" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="C2" s="56"/>
+      <c r="D2" s="57"/>
+    </row>
+    <row r="3" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B3" s="40" t="s">
         <v>2</v>
       </c>
@@ -3069,7 +3043,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="4" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B4" s="17" t="s">
         <v>4</v>
       </c>
@@ -3081,7 +3055,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B5" s="38" t="s">
         <v>56</v>
       </c>
@@ -3093,7 +3067,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="6" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B6" s="38" t="s">
         <v>7</v>
       </c>
@@ -3105,7 +3079,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="7" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B7" s="38" t="s">
         <v>94</v>
       </c>
@@ -3117,7 +3091,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="8" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B8" s="38" t="s">
         <v>83</v>
       </c>
@@ -3129,7 +3103,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="9" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B9" s="38" t="s">
         <v>84</v>
       </c>
@@ -3141,7 +3115,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="10" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B10" s="38" t="s">
         <v>85</v>
       </c>
@@ -3153,7 +3127,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="11" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B11" s="17" t="s">
         <v>86</v>
       </c>
@@ -3165,7 +3139,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="12" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B12" s="38" t="s">
         <v>44</v>
       </c>
@@ -3177,7 +3151,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="13" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B13" s="38" t="s">
         <v>116</v>
       </c>
@@ -3189,7 +3163,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="14" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B14" s="17" t="s">
         <v>96</v>
       </c>
@@ -3201,7 +3175,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="15" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B15" s="17" t="s">
         <v>97</v>
       </c>
@@ -3213,7 +3187,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="16" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B16" s="17" t="s">
         <v>98</v>
       </c>
@@ -3225,7 +3199,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="17" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B17" s="17" t="s">
         <v>82</v>
       </c>
@@ -3237,7 +3211,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="18" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B18" s="17" t="s">
         <v>99</v>
       </c>
@@ -3249,7 +3223,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="19" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B19" s="38" t="s">
         <v>117</v>
       </c>
@@ -3261,7 +3235,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="20" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B20" s="17" t="s">
         <v>118</v>
       </c>
@@ -3273,7 +3247,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="21" spans="2:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="2:6" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B21" s="17"/>
       <c r="C21" s="16">
         <f>SUM(C4:C20)</f>
@@ -3284,20 +3258,20 @@
         <v>46500</v>
       </c>
     </row>
-    <row r="22" spans="2:6" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="2:6" ht="17" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B22" s="39"/>
       <c r="C22" s="25"/>
       <c r="D22" s="31"/>
     </row>
-    <row r="23" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B23" s="2"/>
     </row>
-    <row r="25" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B25" s="3" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="26" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B26" s="3" t="s">
         <v>120</v>
       </c>
@@ -3313,22 +3287,22 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CE339C66-3CA4-4739-A6A3-BB056C0B94A4}">
   <dimension ref="B1:F15"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="7.42578125" customWidth="1"/>
+    <col min="1" max="1" width="7.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="2" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B2" s="49" t="s">
+    <row r="1" spans="2:6" ht="16" thickBot="1" x14ac:dyDescent="0.25"/>
+    <row r="2" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B2" s="55" t="s">
         <v>90</v>
       </c>
-      <c r="C2" s="50"/>
-      <c r="D2" s="50"/>
-      <c r="E2" s="50"/>
-      <c r="F2" s="51"/>
-    </row>
-    <row r="3" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="C2" s="56"/>
+      <c r="D2" s="56"/>
+      <c r="E2" s="56"/>
+      <c r="F2" s="57"/>
+    </row>
+    <row r="3" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B3" s="58" t="s">
         <v>87</v>
       </c>
@@ -3337,13 +3311,13 @@
       <c r="E3" s="59"/>
       <c r="F3" s="60"/>
     </row>
-    <row r="4" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B4" s="40" t="s">
         <v>80</v>
       </c>
       <c r="F4" s="35"/>
     </row>
-    <row r="5" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B5" s="17" t="s">
         <v>82</v>
       </c>
@@ -3351,17 +3325,17 @@
         <v>9900</v>
       </c>
     </row>
-    <row r="6" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B6" s="17"/>
       <c r="F6" s="35"/>
     </row>
-    <row r="7" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B7" s="40" t="s">
         <v>81</v>
       </c>
       <c r="F7" s="35"/>
     </row>
-    <row r="8" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B8" s="43" t="s">
         <v>44</v>
       </c>
@@ -3370,7 +3344,7 @@
       </c>
       <c r="F8" s="35"/>
     </row>
-    <row r="9" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B9" s="43" t="s">
         <v>83</v>
       </c>
@@ -3379,7 +3353,7 @@
       </c>
       <c r="F9" s="35"/>
     </row>
-    <row r="10" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B10" s="43" t="s">
         <v>84</v>
       </c>
@@ -3388,7 +3362,7 @@
       </c>
       <c r="F10" s="35"/>
     </row>
-    <row r="11" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B11" s="43" t="s">
         <v>85</v>
       </c>
@@ -3397,7 +3371,7 @@
       </c>
       <c r="F11" s="35"/>
     </row>
-    <row r="12" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B12" s="44" t="s">
         <v>86</v>
       </c>
@@ -3406,7 +3380,7 @@
       </c>
       <c r="F12" s="35"/>
     </row>
-    <row r="13" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B13" s="44" t="s">
         <v>89</v>
       </c>
@@ -3416,7 +3390,7 @@
         <v>7000</v>
       </c>
     </row>
-    <row r="14" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B14" s="45" t="s">
         <v>88</v>
       </c>
@@ -3424,7 +3398,7 @@
         <v>2900</v>
       </c>
     </row>
-    <row r="15" spans="2:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="2:6" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B15" s="36"/>
       <c r="C15" s="30"/>
       <c r="D15" s="30"/>
@@ -3443,22 +3417,22 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F75FFC87-7B79-4AF4-90E9-13BD22AE4B86}">
   <dimension ref="B1:H36"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="2" max="2" width="35.85546875" customWidth="1"/>
+    <col min="2" max="2" width="35.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="2" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B2" s="49" t="s">
+    <row r="1" spans="2:8" ht="16" thickBot="1" x14ac:dyDescent="0.25"/>
+    <row r="2" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B2" s="55" t="s">
         <v>91</v>
       </c>
-      <c r="C2" s="50"/>
-      <c r="D2" s="50"/>
-      <c r="E2" s="50"/>
-      <c r="F2" s="51"/>
-    </row>
-    <row r="3" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="C2" s="56"/>
+      <c r="D2" s="56"/>
+      <c r="E2" s="56"/>
+      <c r="F2" s="57"/>
+    </row>
+    <row r="3" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B3" s="58" t="s">
         <v>92</v>
       </c>
@@ -3467,13 +3441,13 @@
       <c r="E3" s="59"/>
       <c r="F3" s="60"/>
     </row>
-    <row r="4" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B4" s="17" t="s">
         <v>105</v>
       </c>
       <c r="F4" s="35"/>
     </row>
-    <row r="5" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B5" s="17" t="s">
         <v>106</v>
       </c>
@@ -3481,7 +3455,7 @@
         <v>23500</v>
       </c>
     </row>
-    <row r="6" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B6" s="38" t="s">
         <v>56</v>
       </c>
@@ -3489,7 +3463,7 @@
         <v>2500</v>
       </c>
     </row>
-    <row r="7" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B7" s="38" t="s">
         <v>7</v>
       </c>
@@ -3497,11 +3471,11 @@
         <v>500</v>
       </c>
     </row>
-    <row r="8" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B8" s="38"/>
       <c r="F8" s="21"/>
     </row>
-    <row r="9" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B9" s="17" t="s">
         <v>107</v>
       </c>
@@ -3510,17 +3484,17 @@
         <v>26500</v>
       </c>
     </row>
-    <row r="10" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B10" s="17"/>
       <c r="F10" s="21"/>
     </row>
-    <row r="11" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B11" s="38" t="s">
         <v>108</v>
       </c>
       <c r="F11" s="21"/>
     </row>
-    <row r="12" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B12" s="38" t="s">
         <v>94</v>
       </c>
@@ -3530,7 +3504,7 @@
       <c r="F12" s="35"/>
       <c r="H12" s="20"/>
     </row>
-    <row r="13" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B13" s="38" t="s">
         <v>93</v>
       </c>
@@ -3539,7 +3513,7 @@
       </c>
       <c r="F13" s="21"/>
     </row>
-    <row r="14" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B14" s="38" t="s">
         <v>111</v>
       </c>
@@ -3548,12 +3522,12 @@
         <v>11800</v>
       </c>
     </row>
-    <row r="15" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B15" s="38"/>
       <c r="E15" s="20"/>
       <c r="F15" s="21"/>
     </row>
-    <row r="16" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B16" s="45" t="s">
         <v>95</v>
       </c>
@@ -3562,17 +3536,17 @@
         <v>38300</v>
       </c>
     </row>
-    <row r="17" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B17" s="17"/>
       <c r="F17" s="35"/>
     </row>
-    <row r="18" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B18" s="38" t="s">
         <v>109</v>
       </c>
       <c r="F18" s="35"/>
     </row>
-    <row r="19" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B19" s="17" t="s">
         <v>96</v>
       </c>
@@ -3580,7 +3554,7 @@
         <v>8600</v>
       </c>
     </row>
-    <row r="20" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B20" s="17" t="s">
         <v>97</v>
       </c>
@@ -3588,7 +3562,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="21" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B21" s="17" t="s">
         <v>98</v>
       </c>
@@ -3596,7 +3570,7 @@
         <v>1200</v>
       </c>
     </row>
-    <row r="22" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B22" s="17" t="s">
         <v>99</v>
       </c>
@@ -3604,7 +3578,7 @@
         <v>6000</v>
       </c>
     </row>
-    <row r="23" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B23" s="17" t="s">
         <v>100</v>
       </c>
@@ -3613,21 +3587,21 @@
         <v>16400</v>
       </c>
     </row>
-    <row r="24" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B24" s="17"/>
       <c r="F24" s="21"/>
     </row>
-    <row r="25" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B25" s="38" t="s">
         <v>110</v>
       </c>
       <c r="F25" s="21"/>
     </row>
-    <row r="26" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B26" s="38"/>
       <c r="F26" s="21"/>
     </row>
-    <row r="27" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B27" s="45" t="s">
         <v>100</v>
       </c>
@@ -3636,11 +3610,11 @@
         <v>16400</v>
       </c>
     </row>
-    <row r="28" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B28" s="17"/>
       <c r="F28" s="35"/>
     </row>
-    <row r="29" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="29" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B29" s="40" t="s">
         <v>114</v>
       </c>
@@ -3649,17 +3623,17 @@
         <v>21900</v>
       </c>
     </row>
-    <row r="30" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="30" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B30" s="17"/>
       <c r="F30" s="35"/>
     </row>
-    <row r="31" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="31" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B31" s="17" t="s">
         <v>112</v>
       </c>
       <c r="F31" s="35"/>
     </row>
-    <row r="32" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B32" s="38" t="s">
         <v>24</v>
       </c>
@@ -3668,7 +3642,7 @@
       </c>
       <c r="F32" s="35"/>
     </row>
-    <row r="33" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="33" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B33" s="38" t="s">
         <v>115</v>
       </c>
@@ -3677,7 +3651,7 @@
       </c>
       <c r="F33" s="35"/>
     </row>
-    <row r="34" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="34" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B34" s="17" t="s">
         <v>101</v>
       </c>
@@ -3686,7 +3660,7 @@
       </c>
       <c r="F34" s="35"/>
     </row>
-    <row r="35" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="35" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B35" s="40" t="s">
         <v>113</v>
       </c>
@@ -3694,7 +3668,7 @@
         <v>21900</v>
       </c>
     </row>
-    <row r="36" spans="2:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="2:6" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B36" s="36"/>
       <c r="C36" s="30"/>
       <c r="D36" s="30"/>

--- a/ACCY122/Assessment II/Oceanview Pilates Studio  - Calculation.xlsx
+++ b/ACCY122/Assessment II/Oceanview Pilates Studio  - Calculation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/joseph/Desktop/SIM-UOW-Mods/ACCY122/Assessment II/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D679934F-6734-8349-BE83-A4234EEE4C3A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{106FEE98-557F-4943-B9FD-977A2A278B72}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="500" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="310" uniqueCount="130">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="310" uniqueCount="131">
   <si>
     <t>Ref</t>
   </si>
@@ -430,6 +430,9 @@
   </si>
   <si>
     <t>Equity</t>
+  </si>
+  <si>
+    <t>TOTAL CURRENT LIABILITIES</t>
   </si>
 </sst>
 </file>
@@ -747,6 +750,33 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -755,33 +785,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1181,20 +1184,20 @@
   <sheetData>
     <row r="1" spans="2:12" ht="16" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="2" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B2" s="52" t="s">
+      <c r="B2" s="55" t="s">
         <v>3</v>
       </c>
-      <c r="C2" s="53"/>
-      <c r="D2" s="53"/>
-      <c r="E2" s="53"/>
-      <c r="F2" s="54"/>
-      <c r="H2" s="52" t="s">
+      <c r="C2" s="56"/>
+      <c r="D2" s="56"/>
+      <c r="E2" s="56"/>
+      <c r="F2" s="57"/>
+      <c r="H2" s="55" t="s">
         <v>37</v>
       </c>
-      <c r="I2" s="53"/>
-      <c r="J2" s="53"/>
-      <c r="K2" s="53"/>
-      <c r="L2" s="54"/>
+      <c r="I2" s="56"/>
+      <c r="J2" s="56"/>
+      <c r="K2" s="56"/>
+      <c r="L2" s="57"/>
     </row>
     <row r="3" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B3" s="5" t="s">
@@ -1899,12 +1902,12 @@
   <sheetData>
     <row r="1" spans="2:15" ht="16" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="2" spans="2:15" x14ac:dyDescent="0.2">
-      <c r="B2" s="49" t="s">
+      <c r="B2" s="58" t="s">
         <v>58</v>
       </c>
-      <c r="C2" s="50"/>
-      <c r="D2" s="50"/>
-      <c r="E2" s="51"/>
+      <c r="C2" s="59"/>
+      <c r="D2" s="59"/>
+      <c r="E2" s="60"/>
       <c r="G2" s="27" t="s">
         <v>61</v>
       </c>
@@ -3022,11 +3025,11 @@
   <sheetData>
     <row r="1" spans="2:6" ht="16" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="2" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B2" s="55" t="s">
+      <c r="B2" s="49" t="s">
         <v>75</v>
       </c>
-      <c r="C2" s="56"/>
-      <c r="D2" s="57"/>
+      <c r="C2" s="50"/>
+      <c r="D2" s="51"/>
     </row>
     <row r="3" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B3" s="40" t="s">
@@ -3294,22 +3297,22 @@
   <sheetData>
     <row r="1" spans="2:6" ht="16" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="2" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B2" s="55" t="s">
+      <c r="B2" s="49" t="s">
         <v>90</v>
       </c>
-      <c r="C2" s="56"/>
-      <c r="D2" s="56"/>
-      <c r="E2" s="56"/>
-      <c r="F2" s="57"/>
+      <c r="C2" s="50"/>
+      <c r="D2" s="50"/>
+      <c r="E2" s="50"/>
+      <c r="F2" s="51"/>
     </row>
     <row r="3" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B3" s="58" t="s">
+      <c r="B3" s="52" t="s">
         <v>87</v>
       </c>
-      <c r="C3" s="59"/>
-      <c r="D3" s="59"/>
-      <c r="E3" s="59"/>
-      <c r="F3" s="60"/>
+      <c r="C3" s="53"/>
+      <c r="D3" s="53"/>
+      <c r="E3" s="53"/>
+      <c r="F3" s="54"/>
     </row>
     <row r="4" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B4" s="40" t="s">
@@ -3424,22 +3427,22 @@
   <sheetData>
     <row r="1" spans="2:8" ht="16" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="2" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B2" s="55" t="s">
+      <c r="B2" s="49" t="s">
         <v>91</v>
       </c>
-      <c r="C2" s="56"/>
-      <c r="D2" s="56"/>
-      <c r="E2" s="56"/>
-      <c r="F2" s="57"/>
+      <c r="C2" s="50"/>
+      <c r="D2" s="50"/>
+      <c r="E2" s="50"/>
+      <c r="F2" s="51"/>
     </row>
     <row r="3" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B3" s="58" t="s">
+      <c r="B3" s="52" t="s">
         <v>92</v>
       </c>
-      <c r="C3" s="59"/>
-      <c r="D3" s="59"/>
-      <c r="E3" s="59"/>
-      <c r="F3" s="60"/>
+      <c r="C3" s="53"/>
+      <c r="D3" s="53"/>
+      <c r="E3" s="53"/>
+      <c r="F3" s="54"/>
     </row>
     <row r="4" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B4" s="17" t="s">
@@ -3580,7 +3583,7 @@
     </row>
     <row r="23" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B23" s="17" t="s">
-        <v>100</v>
+        <v>130</v>
       </c>
       <c r="F23" s="21">
         <f>SUM(F19:F22)</f>

--- a/ACCY122/Assessment II/Oceanview Pilates Studio  - Calculation.xlsx
+++ b/ACCY122/Assessment II/Oceanview Pilates Studio  - Calculation.xlsx
@@ -1,23 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10412"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10419"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/joseph/Desktop/SIM-UOW-Mods/ACCY122/Assessment II/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{106FEE98-557F-4943-B9FD-977A2A278B72}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{350E10AE-CA87-7245-802C-FDC65AAAF9A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="500" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="33600" windowHeight="18700" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Journal" sheetId="1" r:id="rId1"/>
     <sheet name="Ledger" sheetId="2" r:id="rId2"/>
     <sheet name="Trial Balance" sheetId="3" r:id="rId3"/>
-    <sheet name="Income Statement" sheetId="4" r:id="rId4"/>
-    <sheet name="Balance Sheet" sheetId="5" r:id="rId5"/>
+    <sheet name="Closing Entry" sheetId="6" r:id="rId4"/>
+    <sheet name="Income Statement" sheetId="4" r:id="rId5"/>
+    <sheet name="Balance Sheet" sheetId="5" r:id="rId6"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -40,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="310" uniqueCount="131">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="341" uniqueCount="150">
   <si>
     <t>Ref</t>
   </si>
@@ -433,6 +434,63 @@
   </si>
   <si>
     <t>TOTAL CURRENT LIABILITIES</t>
+  </si>
+  <si>
+    <t>Closing Entries</t>
+  </si>
+  <si>
+    <t>DR ($)</t>
+  </si>
+  <si>
+    <t>CR ($)</t>
+  </si>
+  <si>
+    <t>Profit &amp; Loss Summary</t>
+  </si>
+  <si>
+    <t>(Close Revenue Account)</t>
+  </si>
+  <si>
+    <t>(Close Expense Account)</t>
+  </si>
+  <si>
+    <t>(Xfer P/L to Capital)</t>
+  </si>
+  <si>
+    <t>Drawings</t>
+  </si>
+  <si>
+    <t>(Close Drawings Account)</t>
+  </si>
+  <si>
+    <t>deposit = receive money</t>
+  </si>
+  <si>
+    <t>purchase policy = spend money</t>
+  </si>
+  <si>
+    <t>purchase on credit = bill</t>
+  </si>
+  <si>
+    <t>issue invoice = invoice</t>
+  </si>
+  <si>
+    <t>paid wages / expense = spend money</t>
+  </si>
+  <si>
+    <t>short term loan = receive money</t>
+  </si>
+  <si>
+    <t>ref 8 - existing invoice</t>
+  </si>
+  <si>
+    <t>ref 9 - existing invoice</t>
+  </si>
+  <si>
+    <t>ref 10 - receive money</t>
+  </si>
+  <si>
+    <t>ref 11 &amp; 12 - spend money</t>
   </si>
 </sst>
 </file>
@@ -628,7 +686,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="61">
+  <cellXfs count="68">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -785,6 +843,21 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1682,7 +1755,7 @@
       </c>
       <c r="F32" s="6"/>
     </row>
-    <row r="33" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B33" s="5"/>
       <c r="D33" s="8" t="s">
         <v>10</v>
@@ -1691,14 +1764,14 @@
         <v>600</v>
       </c>
     </row>
-    <row r="34" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B34" s="5"/>
       <c r="D34" s="9" t="s">
         <v>20</v>
       </c>
       <c r="F34" s="6"/>
     </row>
-    <row r="35" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B35" s="5">
         <v>11</v>
       </c>
@@ -1713,7 +1786,7 @@
       </c>
       <c r="F35" s="6"/>
     </row>
-    <row r="36" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="36" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B36" s="5"/>
       <c r="D36" s="8" t="s">
         <v>21</v>
@@ -1721,15 +1794,21 @@
       <c r="F36" s="6">
         <v>2400</v>
       </c>
-    </row>
-    <row r="37" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="H36" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="37" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B37" s="5"/>
       <c r="D37" s="9" t="s">
         <v>26</v>
       </c>
       <c r="F37" s="6"/>
-    </row>
-    <row r="38" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="H37" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="38" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B38" s="5">
         <v>12</v>
       </c>
@@ -1743,8 +1822,11 @@
         <v>2200</v>
       </c>
       <c r="F38" s="6"/>
-    </row>
-    <row r="39" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="H38" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="39" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B39" s="5"/>
       <c r="D39" s="8" t="s">
         <v>10</v>
@@ -1752,15 +1834,21 @@
       <c r="F39" s="6">
         <v>2200</v>
       </c>
-    </row>
-    <row r="40" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="H39" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="40" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B40" s="5"/>
       <c r="D40" s="9" t="s">
         <v>16</v>
       </c>
       <c r="F40" s="6"/>
-    </row>
-    <row r="41" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="H40" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="41" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B41" s="5">
         <v>13</v>
       </c>
@@ -1774,8 +1862,11 @@
         <v>600</v>
       </c>
       <c r="F41" s="6"/>
-    </row>
-    <row r="42" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="H41" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="42" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B42" s="5"/>
       <c r="D42" s="2" t="s">
         <v>10</v>
@@ -1783,8 +1874,11 @@
       <c r="F42" s="6">
         <v>600</v>
       </c>
-    </row>
-    <row r="43" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="H42" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="43" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B43" s="5"/>
       <c r="C43" s="1" t="s">
         <v>9</v>
@@ -1793,8 +1887,11 @@
         <v>35</v>
       </c>
       <c r="F43" s="6"/>
-    </row>
-    <row r="44" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="H43" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="44" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B44" s="5">
         <v>14</v>
       </c>
@@ -1808,8 +1905,11 @@
         <v>1000</v>
       </c>
       <c r="F44" s="6"/>
-    </row>
-    <row r="45" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="H44" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="45" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B45" s="5"/>
       <c r="D45" s="10" t="s">
         <v>10</v>
@@ -1817,20 +1917,23 @@
       <c r="F45" s="6">
         <v>1000</v>
       </c>
-    </row>
-    <row r="46" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="H45" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="46" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B46" s="5"/>
       <c r="D46" s="9" t="s">
         <v>25</v>
       </c>
       <c r="F46" s="6"/>
     </row>
-    <row r="47" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B47" s="5"/>
       <c r="D47" s="2"/>
       <c r="F47" s="6"/>
     </row>
-    <row r="48" spans="2:6" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="2:8" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B48" s="5"/>
       <c r="D48" s="2" t="s">
         <v>33</v>
@@ -3288,6 +3391,200 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{76D72D53-F926-FF4B-B4DD-0BD440883AE2}">
+  <dimension ref="B1:D23"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="2" max="2" width="19.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="2:4" ht="16" thickBot="1" x14ac:dyDescent="0.25"/>
+    <row r="2" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B2" s="49" t="s">
+        <v>3</v>
+      </c>
+      <c r="C2" s="50"/>
+      <c r="D2" s="51"/>
+    </row>
+    <row r="3" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B3" s="61" t="s">
+        <v>131</v>
+      </c>
+      <c r="C3" s="65"/>
+      <c r="D3" s="62"/>
+    </row>
+    <row r="4" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B4" s="17" t="s">
+        <v>51</v>
+      </c>
+      <c r="C4" s="66" t="s">
+        <v>132</v>
+      </c>
+      <c r="D4" s="35" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="5" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B5" s="17" t="s">
+        <v>82</v>
+      </c>
+      <c r="C5" s="67">
+        <v>9900</v>
+      </c>
+      <c r="D5" s="21"/>
+    </row>
+    <row r="6" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B6" s="44" t="s">
+        <v>134</v>
+      </c>
+      <c r="C6" s="67"/>
+      <c r="D6" s="21">
+        <v>9900</v>
+      </c>
+    </row>
+    <row r="7" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B7" s="63" t="s">
+        <v>135</v>
+      </c>
+      <c r="C7" s="67"/>
+      <c r="D7" s="21"/>
+    </row>
+    <row r="8" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B8" s="17"/>
+      <c r="C8" s="67"/>
+      <c r="D8" s="21"/>
+    </row>
+    <row r="9" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B9" s="17" t="s">
+        <v>134</v>
+      </c>
+      <c r="C9" s="67">
+        <v>7000</v>
+      </c>
+      <c r="D9" s="21"/>
+    </row>
+    <row r="10" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B10" s="38" t="s">
+        <v>83</v>
+      </c>
+      <c r="C10" s="67"/>
+      <c r="D10" s="21">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="11" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B11" s="38" t="s">
+        <v>84</v>
+      </c>
+      <c r="C11" s="67"/>
+      <c r="D11" s="21">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="12" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B12" s="38" t="s">
+        <v>85</v>
+      </c>
+      <c r="C12" s="67"/>
+      <c r="D12" s="21">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="13" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B13" s="17" t="s">
+        <v>86</v>
+      </c>
+      <c r="C13" s="67"/>
+      <c r="D13" s="21">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="14" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B14" s="38" t="s">
+        <v>44</v>
+      </c>
+      <c r="C14" s="67"/>
+      <c r="D14" s="21">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="15" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B15" s="63" t="s">
+        <v>136</v>
+      </c>
+      <c r="C15" s="67"/>
+      <c r="D15" s="21"/>
+    </row>
+    <row r="16" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B16" s="63"/>
+      <c r="C16" s="67"/>
+      <c r="D16" s="21"/>
+    </row>
+    <row r="17" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B17" s="17" t="s">
+        <v>134</v>
+      </c>
+      <c r="C17" s="67">
+        <v>2900</v>
+      </c>
+      <c r="D17" s="21"/>
+    </row>
+    <row r="18" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B18" s="44" t="s">
+        <v>11</v>
+      </c>
+      <c r="C18" s="67"/>
+      <c r="D18" s="21">
+        <v>2900</v>
+      </c>
+    </row>
+    <row r="19" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B19" s="63" t="s">
+        <v>137</v>
+      </c>
+      <c r="C19" s="67"/>
+      <c r="D19" s="21"/>
+    </row>
+    <row r="20" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B20" s="63"/>
+      <c r="C20" s="67"/>
+      <c r="D20" s="21"/>
+    </row>
+    <row r="21" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B21" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="C21" s="67">
+        <v>1000</v>
+      </c>
+      <c r="D21" s="21"/>
+    </row>
+    <row r="22" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B22" s="44" t="s">
+        <v>138</v>
+      </c>
+      <c r="C22" s="67"/>
+      <c r="D22" s="21">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="23" spans="2:4" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B23" s="64" t="s">
+        <v>139</v>
+      </c>
+      <c r="C23" s="25"/>
+      <c r="D23" s="31"/>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="B3:D3"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CE339C66-3CA4-4739-A6A3-BB056C0B94A4}">
   <dimension ref="B1:F15"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
@@ -3417,7 +3714,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F75FFC87-7B79-4AF4-90E9-13BD22AE4B86}">
   <dimension ref="B1:H36"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
